--- a/tests/testthat/golden/P02.xlsx
+++ b/tests/testthat/golden/P02.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="60" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="120" uniqueCount="44">
   <si>
     <t>Table P2. First Ten Cars</t>
   </si>
@@ -151,7 +151,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -184,8 +184,18 @@
       <b/>
       <name val="Arial"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -197,8 +207,14 @@
         <fgColor rgb="FFEDF2F9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDF2F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -235,11 +251,25 @@
       <bottom style="medium"/>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium"/>
+      <bottom style="medium"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -313,6 +343,30 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -334,206 +388,206 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="B1" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="27" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="12" t="s">
+      <c r="A2" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="26" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="A3" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="23" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="16" t="s">
+      <c r="A4" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="24" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="A5" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="23" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="16" t="s">
+      <c r="A6" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="24" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="5" t="s">
+      <c r="A7" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="23" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="16" t="s">
+      <c r="A8" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="24" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="5" t="s">
+      <c r="A9" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="23" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="16" t="s">
+      <c r="A10" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="24" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="5" t="s">
+      <c r="A11" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="23" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="18" t="s">
+      <c r="A12" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="25" t="s">
         <v>43</v>
       </c>
     </row>
